--- a/output/pdf_financials_xlsx/USHA.xlsx
+++ b/output/pdf_financials_xlsx/USHA.xlsx
@@ -892,19 +892,19 @@
         <v>-0.178959</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.467622</v>
+        <v>-0.467622</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.9424400000000001</v>
+        <v>-0.9424400000000001</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>2.977621</v>
+        <v>-2.977621</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>3.433859</v>
+        <v>-3.433859</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.162515</v>
+        <v>-0.162515</v>
       </c>
     </row>
     <row r="17">
@@ -1048,19 +1048,19 @@
         <v>-0.178959</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.467622</v>
+        <v>-0.467622</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.9424400000000001</v>
+        <v>-0.9424400000000001</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>2.977621</v>
+        <v>-2.977621</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>3.433859</v>
+        <v>-3.433859</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.162515</v>
+        <v>-0.162515</v>
       </c>
     </row>
     <row r="21">
@@ -1141,19 +1141,19 @@
         <v>-0.178959</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.467622</v>
+        <v>-0.467622</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.9424400000000001</v>
+        <v>-0.9424400000000001</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>2.977621</v>
+        <v>-2.977621</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>3.433859</v>
+        <v>-3.433859</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.162515</v>
+        <v>-0.162515</v>
       </c>
     </row>
     <row r="24">
@@ -1240,16 +1240,16 @@
         <v>-4.473975</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>11.69055</v>
+        <v>-11.69055</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>18.8488</v>
+        <v>-18.8488</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>33.084678</v>
+        <v>-33.084678</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>49.055129</v>
+        <v>-49.055129</v>
       </c>
       <c r="I26" s="1" t="inlineStr">
         <is>
@@ -1273,19 +1273,19 @@
         <v>-0.178959</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.467622</v>
+        <v>-0.467622</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.9424400000000001</v>
+        <v>-0.9424400000000001</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>2.977621</v>
+        <v>-2.977621</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>3.433859</v>
+        <v>-3.433859</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.162515</v>
+        <v>-0.162515</v>
       </c>
     </row>
     <row r="28">
@@ -1335,19 +1335,19 @@
         <v>-0.178959</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.467622</v>
+        <v>-0.467622</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.9424400000000001</v>
+        <v>-0.9424400000000001</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>2.977621</v>
+        <v>-2.977621</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>3.433859</v>
+        <v>-3.433859</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.162515</v>
+        <v>-0.162515</v>
       </c>
     </row>
     <row r="30">
@@ -1413,19 +1413,19 @@
         <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -3402,25 +3402,25 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.042201</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.042201</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.120799</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.294382</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.53017</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.056219</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.012823</v>
       </c>
     </row>
     <row r="93">
@@ -5398,7 +5398,11 @@
           <t>Reserves (Note 6c)</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -5942,7 +5946,11 @@
           <t>Reserves (Note 5d)</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -6154,7 +6162,11 @@
           <t>Reserves (Note 5c)</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -6264,7 +6276,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -9637,19 +9653,19 @@
         <v>-0.178959</v>
       </c>
       <c r="H91" s="5" t="n">
-        <v>0.467622</v>
+        <v>-0.467622</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>0.9424400000000001</v>
+        <v>-0.9424400000000001</v>
       </c>
       <c r="J91" s="5" t="n">
-        <v>2.977621</v>
+        <v>-2.977621</v>
       </c>
       <c r="K91" s="5" t="n">
-        <v>3.433859</v>
+        <v>-3.433859</v>
       </c>
       <c r="L91" s="5" t="n">
-        <v>0.162515</v>
+        <v>-0.162515</v>
       </c>
     </row>
     <row r="92">

--- a/output/pdf_financials_xlsx/USHA.xlsx
+++ b/output/pdf_financials_xlsx/USHA.xlsx
@@ -762,19 +762,19 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001088</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.002267</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000433</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000703</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.016592</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
@@ -1267,19 +1267,19 @@
         <v>-0.010004</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.091472</v>
+        <v>-0.09038400000000001</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.178959</v>
+        <v>-0.176692</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.467622</v>
+        <v>-0.467189</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.9424400000000001</v>
+        <v>-0.941737</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-2.977621</v>
+        <v>-2.961029</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-3.433859</v>
@@ -1329,19 +1329,19 @@
         <v>-0.010004</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.091472</v>
+        <v>-0.09038400000000001</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.178959</v>
+        <v>-0.176692</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.467622</v>
+        <v>-0.467189</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.9424400000000001</v>
+        <v>-0.941737</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-2.977621</v>
+        <v>-2.961029</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-3.433859</v>
@@ -1489,16 +1489,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.109996</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.176701</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.427529</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.221758</v>
       </c>
       <c r="F34" s="3" t="n">
         <v>1.170795</v>
@@ -1551,16 +1551,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.109996</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.176701</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.427529</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.221758</v>
       </c>
       <c r="F36" s="3" t="n">
         <v>1.170795</v>
@@ -1923,16 +1923,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.109996</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.180796</v>
+        <v>0.004095</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.427529</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.241643</v>
+        <v>0.019885</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0.206837</v>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E23" s="5" t="n">
@@ -11724,7 +11724,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
